--- a/public/crawlability-cheryisrael-september-2026.xlsx
+++ b/public/crawlability-cheryisrael-september-2026.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. עימוד של ארכיון תגית שמצביע על עמודים שאינם קיימים; לתקן את מנגנון העימוד בתבנית התגית.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). עימוד של ארכיון תגית שמצביע על עמודים שאינם קיימים; לתקן את מנגנון העימוד בתבנית התגית.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. ראו עמוד 2.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). ראו עמוד 2.</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. ראו עמוד 2.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). ראו עמוד 2.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">

--- a/public/crawlability-cheryisrael-september-2026.xlsx
+++ b/public/crawlability-cheryisrael-september-2026.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ב-Search Console מדווחות שגיאות במפת האתר; לבדוק בדוח Sitemaps.</t>
+          <t>my.cheryisrael.co.il: עותק של אתר הבית, מוגן רק ב-canonical לדומיין הראשי. להגן בסיסמה או להגדיר noindex; לברר את ייעודו.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>my.cheryisrael.co.il: עותק של אתר הבית, מוגן רק ב-canonical לדומיין הראשי. להגן בסיסמה או להגדיר noindex; לברר את ייעודו.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות (הבולטת: https://cheryisrael.co.il/blog/page/1/, 5 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות (הבולטת: https://cheryisrael.co.il/blog/page/1/, 5 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>חסימות סורק (403/429/timeout) לבדיקה: 77 כתובות (הבולטת: https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?d…, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -572,14 +572,14 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: https://www.cheryisrael.co.il/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>ההגשה של https://cheryisrael.co.il/category-sitemap.xml ב-Search Console מדווחת שגיאה והקובץ אינו קיים עוד במפת האתר; להסיר את ההגשה הישנה.</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות (הבולטת: https://cheryisrael.co.il/blog/suv, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: https://www.cheryisrael.co.il/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -617,14 +617,14 @@
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>לאשר ש-16 העמודים המוגדרים noindex אכן אמורים להישאר מחוץ לאינדקס.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות (הבולטת: https://cheryisrael.co.il/blog/suv, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>חסימות סורק (403/429/timeout) לבדיקה: 77 כתובות (הבולטת: https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?d, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>לאשר ש-16 העמודים המוגדרים noindex אכן אמורים להישאר מחוץ לאינדקס.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-cheryisrael-september-2026.xlsx
+++ b/public/crawlability-cheryisrael-september-2026.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>חסימות סורק (403/429/timeout) לבדיקה: 77 כתובות (הבולטת: https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?d…, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>חסימות סורק (403/429/timeout) לבדיקה: 77 כתובות (הבולטת: https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?d…, ללא קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-cheryisrael-september-2026.xlsx
+++ b/public/crawlability-cheryisrael-september-2026.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 5 כתובות (הבולטת: https://cheryisrael.co.il/tag/car-safety-system/page/2/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): 5 כתובות; הבולטת https://cheryisrael.co.il/tag/car-safety-system/page/2/ (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות (הבולטת: https://cheryisrael.co.il/blog/page/1/, 5 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות; הבולטת https://cheryisrael.co.il/blog/page/1/ (5 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>חסימות סורק (403/429/timeout) לבדיקה: 77 כתובות (הבולטת: https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?d…, ללא קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>חסימות סורק (403/429/timeout) לבדיקה: 77 כתובות; הבולטת https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?d… (ללא קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: https://www.cheryisrael.co.il/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת; הבולטת https://www.cheryisrael.co.il/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות (הבולטת: https://cheryisrael.co.il/blog/suv, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות; הבולטת https://cheryisrael.co.il/blog/suv (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). עימוד של ארכיון תגית שמצביע על עמודים שאינם קיימים; לתקן את מנגנון העימוד בתבנית התגית.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). עימוד של ארכיון תגית שמצביע על עמודים שאינם קיימים; לתקן את מנגנון העימוד בתבנית התגית.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). ראו עמוד 2.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). ראו עמוד 2.</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). ראו עמוד 2.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). ראו עמוד 2.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">

--- a/public/crawlability-cheryisrael-september-2026.xlsx
+++ b/public/crawlability-cheryisrael-september-2026.xlsx
@@ -42,7 +42,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +71,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
@@ -92,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -109,13 +104,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -483,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -534,7 +526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>my.cheryisrael.co.il: עותק של אתר הבית, מוגן רק ב-canonical לדומיין הראשי. להגן בסיסמה או להגדיר noindex; לברר את ייעודו.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות; הבולטת https://cheryisrael.co.il/blog/page/1/ (5 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -542,14 +534,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות; הבולטת https://cheryisrael.co.il/blog/page/1/ (5 קישורים נכנסים).</t>
+          <t>ההגשה של https://cheryisrael.co.il/category-sitemap.xml ב-Search Console מדווחת שגיאה והקובץ אינו קיים עוד במפת האתר; להסיר את ההגשה הישנה.</t>
         </is>
       </c>
     </row>
@@ -557,14 +549,14 @@
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>חסימות סורק (403/429/timeout) לבדיקה: 77 כתובות; הבולטת https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?d… (ללא קישורים נכנסים).</t>
+          <t>campaigns.cheryisrael.co.il: תת-דומיין פעיל עם תבנית PHP ריקה. להסיר את הרשומה ב-DNS או להגדיר noindex.</t>
         </is>
       </c>
     </row>
@@ -579,7 +571,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ההגשה של https://cheryisrael.co.il/category-sitemap.xml ב-Search Console מדווחת שגיאה והקובץ אינו קיים עוד במפת האתר; להסיר את ההגשה הישנה.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת; הבולטת https://www.cheryisrael.co.il/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -594,7 +586,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>campaigns.cheryisrael.co.il: תת-דומיין פעיל עם תבנית PHP ריקה. להסיר את הרשומה ב-DNS או להגדיר noindex.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות; הבולטת https://cheryisrael.co.il/blog/suv (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -609,37 +601,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת; הבולטת https://www.cheryisrael.co.il/ (קישור נכנס אחד).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות; הבולטת https://cheryisrael.co.il/blog/suv (2 קישורים נכנסים).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>לאשר ש-16 העמודים המוגדרים noindex אכן אמורים להישאר מחוץ לאינדקס.</t>
+          <t>חסימות סורק (403/429/timeout) לבדיקה: 77 כתובות; הבולטת https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?d… (ללא קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -728,7 +690,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/page/2/</t>
         </is>
@@ -748,7 +710,7 @@
       <c r="F2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/</t>
         </is>
@@ -763,7 +725,7 @@
           <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). עימוד של ארכיון תגית שמצביע על עמודים שאינם קיימים; לתקן את מנגנון העימוד בתבנית התגית.</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/</t>
         </is>
@@ -775,7 +737,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/privacy</t>
         </is>
@@ -795,7 +757,7 @@
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/legal-terms/</t>
         </is>
@@ -818,7 +780,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/page/3/</t>
         </is>
@@ -838,7 +800,7 @@
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/</t>
         </is>
@@ -853,7 +815,7 @@
           <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). ראו עמוד 2.</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/</t>
         </is>
@@ -865,7 +827,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/page/4/</t>
         </is>
@@ -885,7 +847,7 @@
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/</t>
         </is>
@@ -900,7 +862,7 @@
           <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). ראו עמוד 2.</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/tag/car-safety-system/</t>
         </is>
@@ -912,7 +874,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/themes/zemingo-cars-18-12-2022/360/FX-HEV/metallic-black-silver.png</t>
         </is>
@@ -932,7 +894,7 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/models/fx-hev/</t>
         </is>
@@ -1039,7 +1001,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/page/1/</t>
         </is>
@@ -1052,7 +1014,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/</t>
         </is>
@@ -1063,7 +1025,7 @@
       <c r="F2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/page/4/
 https://cheryisrael.co.il/blog/page/2/
@@ -1081,7 +1043,7 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/</t>
         </is>
@@ -1093,7 +1055,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/general/page/1/</t>
         </is>
@@ -1106,7 +1068,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/general/</t>
         </is>
@@ -1117,7 +1079,7 @@
       <c r="F3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/general/page/2/</t>
         </is>
@@ -1132,7 +1094,7 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/general/</t>
         </is>
@@ -1144,7 +1106,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-news/page/1/</t>
         </is>
@@ -1157,7 +1119,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-news/</t>
         </is>
@@ -1168,7 +1130,7 @@
       <c r="F4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-news/page/2/</t>
         </is>
@@ -1183,7 +1145,7 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-news/</t>
         </is>
@@ -1195,7 +1157,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>https://www.cheryisrael.co.il/</t>
         </is>
@@ -1208,7 +1170,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/</t>
         </is>
@@ -1219,7 +1181,7 @@
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/legal-terms/</t>
         </is>
@@ -1234,7 +1196,7 @@
           <t>קישור פנימי לגרסת דומיין לא קנונית (www/ללא www או http). לעדכן את הקישור לכתובת הקנונית.</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/</t>
         </is>
@@ -1246,7 +1208,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/suv</t>
         </is>
@@ -1259,7 +1221,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/suv/</t>
         </is>
@@ -1270,7 +1232,7 @@
       <c r="F6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/crossover-vs-suv/
 https://cheryisrael.co.il/blog/crossover-vs-suv/</t>
@@ -1286,7 +1248,7 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/suv/</t>
         </is>
@@ -1298,7 +1260,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/about</t>
         </is>
@@ -1311,7 +1273,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/about/</t>
         </is>
@@ -1322,7 +1284,7 @@
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/</t>
         </is>
@@ -1337,7 +1299,7 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/about/</t>
         </is>
@@ -1349,7 +1311,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/services-centers</t>
         </is>
@@ -1362,7 +1324,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/services-centers/</t>
         </is>
@@ -1373,7 +1335,7 @@
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/</t>
         </is>
@@ -1388,7 +1350,7 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/services-centers/</t>
         </is>
@@ -1400,7 +1362,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/funding</t>
         </is>
@@ -1413,7 +1375,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/funding/</t>
         </is>
@@ -1424,7 +1386,7 @@
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/</t>
         </is>
@@ -1439,7 +1401,7 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/funding/</t>
         </is>
@@ -1535,7 +1497,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790180201</t>
         </is>
@@ -1567,14 +1529,14 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151393</t>
         </is>
@@ -1606,14 +1568,14 @@
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187697</t>
         </is>
@@ -1645,14 +1607,14 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187774</t>
         </is>
@@ -1684,14 +1646,14 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187431</t>
         </is>
@@ -1723,14 +1685,14 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187660</t>
         </is>
@@ -1762,14 +1724,14 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187772</t>
         </is>
@@ -1801,14 +1763,14 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187787</t>
         </is>
@@ -1840,14 +1802,14 @@
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187503</t>
         </is>
@@ -1879,14 +1841,14 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187711</t>
         </is>
@@ -1918,14 +1880,14 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187694</t>
         </is>
@@ -1957,14 +1919,14 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187532</t>
         </is>
@@ -1996,14 +1958,14 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151874</t>
         </is>
@@ -2035,14 +1997,14 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151871</t>
         </is>
@@ -2074,14 +2036,14 @@
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187527</t>
         </is>
@@ -2113,14 +2075,14 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187447</t>
         </is>
@@ -2152,14 +2114,14 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151398</t>
         </is>
@@ -2191,14 +2153,14 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187781</t>
         </is>
@@ -2230,14 +2192,14 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151403</t>
         </is>
@@ -2269,14 +2231,14 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187708</t>
         </is>
@@ -2308,14 +2270,14 @@
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187700</t>
         </is>
@@ -2347,14 +2309,14 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151877</t>
         </is>
@@ -2386,14 +2348,14 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187583</t>
         </is>
@@ -2425,14 +2387,14 @@
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151396</t>
         </is>
@@ -2464,14 +2426,14 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187779</t>
         </is>
@@ -2503,14 +2465,14 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187493</t>
         </is>
@@ -2542,14 +2504,14 @@
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151455</t>
         </is>
@@ -2581,14 +2543,14 @@
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151401</t>
         </is>
@@ -2620,14 +2582,14 @@
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187777</t>
         </is>
@@ -2659,14 +2621,14 @@
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187705</t>
         </is>
@@ -2698,14 +2660,14 @@
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187703</t>
         </is>
@@ -2737,14 +2699,14 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187603</t>
         </is>
@@ -2776,14 +2738,14 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187584</t>
         </is>
@@ -2815,14 +2777,14 @@
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790161516</t>
         </is>
@@ -2854,14 +2816,14 @@
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187590</t>
         </is>
@@ -2893,14 +2855,14 @@
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187497</t>
         </is>
@@ -2932,14 +2894,14 @@
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187654</t>
         </is>
@@ -2971,14 +2933,14 @@
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187785</t>
         </is>
@@ -3010,14 +2972,14 @@
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187404</t>
         </is>
@@ -3049,14 +3011,14 @@
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187508</t>
         </is>
@@ -3088,14 +3050,14 @@
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187526</t>
         </is>
@@ -3127,14 +3089,14 @@
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187398</t>
         </is>
@@ -3166,14 +3128,14 @@
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187511</t>
         </is>
@@ -3205,14 +3167,14 @@
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187596</t>
         </is>
@@ -3244,14 +3206,14 @@
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187651</t>
         </is>
@@ -3283,14 +3245,14 @@
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790190681</t>
         </is>
@@ -3322,14 +3284,14 @@
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790161513</t>
         </is>
@@ -3361,14 +3323,14 @@
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187587</t>
         </is>
@@ -3400,14 +3362,14 @@
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187538</t>
         </is>
@@ -3439,14 +3401,14 @@
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187657</t>
         </is>
@@ -3478,14 +3440,14 @@
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151833</t>
         </is>
@@ -3517,14 +3479,14 @@
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187529</t>
         </is>
@@ -3556,14 +3518,14 @@
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151830</t>
         </is>
@@ -3595,14 +3557,14 @@
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151824</t>
         </is>
@@ -3634,14 +3596,14 @@
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151769</t>
         </is>
@@ -3673,14 +3635,14 @@
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187520</t>
         </is>
@@ -3712,14 +3674,14 @@
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151817</t>
         </is>
@@ -3751,14 +3713,14 @@
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187600</t>
         </is>
@@ -3790,14 +3752,14 @@
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187647</t>
         </is>
@@ -3829,14 +3791,14 @@
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187593</t>
         </is>
@@ -3868,14 +3830,14 @@
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187644</t>
         </is>
@@ -3907,14 +3869,14 @@
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187641</t>
         </is>
@@ -3946,14 +3908,14 @@
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187514</t>
         </is>
@@ -3985,14 +3947,14 @@
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187535</t>
         </is>
@@ -4024,14 +3986,14 @@
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187523</t>
         </is>
@@ -4063,14 +4025,14 @@
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187499</t>
         </is>
@@ -4102,14 +4064,14 @@
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187505</t>
         </is>
@@ -4141,14 +4103,14 @@
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790190686</t>
         </is>
@@ -4180,14 +4142,14 @@
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187401</t>
         </is>
@@ -4219,14 +4181,14 @@
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187395</t>
         </is>
@@ -4258,14 +4220,14 @@
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790187391</t>
         </is>
@@ -4297,14 +4259,14 @@
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151754</t>
         </is>
@@ -4336,14 +4298,14 @@
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151760</t>
         </is>
@@ -4375,14 +4337,14 @@
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151751</t>
         </is>
@@ -4414,14 +4376,14 @@
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151726</t>
         </is>
@@ -4453,14 +4415,14 @@
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790151757</t>
         </is>
@@ -4492,14 +4454,14 @@
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-content/cache/background-css/1/cheryisrael.co.il/?display_custom_css=css&amp;wpr_t=1790190693</t>
         </is>
@@ -4531,9 +4493,9 @@
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4570,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/sitemap_index.xml</t>
         </is>
@@ -4662,7 +4624,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/sitemap_index.xml</t>
         </is>
@@ -4684,7 +4646,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/post-sitemap.xml</t>
         </is>
@@ -4706,7 +4668,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/page-sitemap.xml</t>
         </is>
@@ -4728,7 +4690,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/products-sitemap.xml</t>
         </is>
@@ -4750,7 +4712,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/sitemap.xml</t>
         </is>
@@ -4772,7 +4734,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/wp-sitemap.xml</t>
         </is>
@@ -4816,7 +4778,7 @@
           <t>קוד 301 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/suv/</t>
         </is>
@@ -4834,7 +4796,7 @@
           <t>קוד 301 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/about/</t>
         </is>
@@ -4852,7 +4814,7 @@
           <t>קוד 301 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/funding/</t>
         </is>
@@ -4870,7 +4832,7 @@
           <t>קוד 301 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/services-centers/</t>
         </is>
@@ -4883,7 +4845,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/</t>
         </is>
@@ -4893,7 +4855,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/ (0 הפניות)</t>
         </is>
@@ -4905,7 +4867,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>http://cheryisrael.co.il/</t>
         </is>
@@ -4915,7 +4877,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/ (1 הפניות)</t>
         </is>
@@ -4927,7 +4889,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>https://www.cheryisrael.co.il/</t>
         </is>
@@ -4937,7 +4899,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/ (1 הפניות)</t>
         </is>
@@ -4949,7 +4911,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>http://www.cheryisrael.co.il/</t>
         </is>
@@ -4959,7 +4921,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/ (1 הפניות)</t>
         </is>
@@ -5012,7 +4974,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/</t>
         </is>
@@ -5030,7 +4992,7 @@
           <t>תקנון צ'רי פלוס - מסלול מימון ובייבאק - ספטמבר 2026 | Chery Israel</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/offer-terms/</t>
         </is>
@@ -5052,7 +5014,7 @@
           <t>תקנון רכבי 0 ק"מ מבעלות ראשונה – ספטמבר 2026 | Chery Israel</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/0km-terms/</t>
         </is>
@@ -5074,7 +5036,7 @@
           <t>תקנון צ'רי מבצעי חגים – ספטמבר 2026 | Chery Israel</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/sales-terms/</t>
         </is>
@@ -5096,7 +5058,7 @@
           <t>תקנון ליסינג פרטי צ'רי – ספטמבר 2026 | Chery Israel</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/lease-terms/</t>
         </is>
@@ -5118,7 +5080,7 @@
           <t>קבוצת Chery נכנסת לראשונה לרשימת Fortune Global 500 | Chery Israel</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/first-time-entry-fortune-global-500/</t>
         </is>
@@ -5140,7 +5102,7 @@
           <t>Chery זוכה להכרה עולמית ופותחת עידן חדש של המותג | Chery Israel</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/chery-gains-global-recognition/</t>
         </is>
@@ -5162,7 +5124,7 @@
           <t>קבוצת צ'רי מכרה 1.23 מיליון יחידות בשנת 2022 | Chery Israel</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/chery-group-achieved-sales-volume-2022/</t>
         </is>
@@ -5184,7 +5146,7 @@
           <t>צ'רי זוכה בפעם השישית באליפות אולימפיאדת האיכות | Chery Israel</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/news-chery-wins-quality-olympics/</t>
         </is>
@@ -5206,7 +5168,7 @@
           <t>צ'רי מאיצה את אסטרטגיית הגלובליזציה שלה | Chery Israel</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/blog/shanghai-motor-show-2023/</t>
         </is>
@@ -5228,7 +5190,7 @@
           <t>חדשות המותג Archives - Chery Israel</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-news/</t>
         </is>
@@ -5250,7 +5212,7 @@
           <t>Chery בנזין Archives - Chery Israel</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-petrol/</t>
         </is>
@@ -5272,7 +5234,7 @@
           <t>Chery היברידי Archives - Chery Israel</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-hybrid/</t>
         </is>
@@ -5294,7 +5256,7 @@
           <t>כללי Archives - Chery Israel</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/general/</t>
         </is>
@@ -5316,7 +5278,7 @@
           <t>Chery חשמלי Archives - Chery Israel</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-electric/</t>
         </is>
@@ -5338,7 +5300,7 @@
           <t>כללי Archives - עמוד 2 מתוך 2 - Chery Israel</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/general/page/2/</t>
         </is>
@@ -5360,7 +5322,7 @@
           <t>חדשות המותג Archives - עמוד 2 מתוך 2 - Chery Israel</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>https://cheryisrael.co.il/category/chery-news/page/2/</t>
         </is>
@@ -5382,7 +5344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5481,7 +5443,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>my.cheryisrael.co.il</t>
+          <t>view.info.cheryisrael.co.il</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -5491,70 +5453,23 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Chery Israel - רכבי צ&amp;#039;רי ישראל - האתר הרשמי</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>index, follow, max-image-preview:large, max-snippet:-1, max-video-preview:-1</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>https://cheryisrael.co.il/</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>עותק של האתר (index, follow)</t>
+          <t>מערכת דיוור</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>עותק של אתר הבית, מוגן רק ב-canonical לדומיין הראשי. להגן בסיסמה או להגדיר noindex; לברר את ייעודו.</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>view.info.cheryisrael.co.il</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>מערכת דיוור</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
           <t>ללא פעולה.</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
